--- a/reporting/RedAndYellow_Analytics.xlsx
+++ b/reporting/RedAndYellow_Analytics.xlsx
@@ -28,7 +28,7 @@
     <t>CRM &amp; Academic Analytics - marketing spend through to student outcomes</t>
   </si>
   <si>
-    <t>Generated 08 September 2026 from the dbt warehouse. Catalogue is real; all people and campaigns are synthetic.</t>
+    <t>Generated 09 September 2026 from the dbt warehouse. Catalogue is real; all people and campaigns are synthetic.</t>
   </si>
   <si>
     <t>1,500,000</t>
@@ -154,10 +154,10 @@
     <t>Paid social</t>
   </si>
   <si>
+    <t>Print</t>
+  </si>
+  <si>
     <t>Webinar</t>
-  </si>
-  <si>
-    <t>Print</t>
   </si>
   <si>
     <t>Programme demand</t>
@@ -1144,10 +1144,10 @@
                   <c:v>Paid social</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Print</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Webinar</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Print</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1186,10 +1186,10 @@
                   <c:v>4552</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>5129</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>4984</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>5129</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,10 +1307,10 @@
                   <c:v>Paid social</c:v>
                 </c:pt>
                 <c:pt idx="9">
+                  <c:v>Print</c:v>
+                </c:pt>
+                <c:pt idx="10">
                   <c:v>Webinar</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Print</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1325,31 +1325,31 @@
                   <c:v>2.29</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.12</c:v>
+                  <c:v>2.13</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2.01</c:v>
+                  <c:v>2.02</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.94</c:v>
+                  <c:v>1.93</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1.85</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1.82</c:v>
+                  <c:v>1.83</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.78</c:v>
+                  <c:v>1.77</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.76</c:v>
+                  <c:v>1.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>1.69</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1.55</c:v>
+                  <c:v>1.56</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>1.55</c:v>
@@ -1517,19 +1517,19 @@
                   <c:v>83.09999999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>82.40000000000001</c:v>
+                  <c:v>82.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>81.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>80.7</c:v>
+                  <c:v>80.8</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>79.90000000000001</c:v>
+                  <c:v>79.8</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>79</c:v>
+                  <c:v>79.09999999999999</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>78.2</c:v>
@@ -1553,19 +1553,19 @@
                   <c:v>73</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>72</c:v>
+                  <c:v>72.2</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>71.40000000000001</c:v>
+                  <c:v>71.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>70.3</c:v>
+                  <c:v>70.40000000000001</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69.5</c:v>
+                  <c:v>69.7</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>68.5</c:v>
+                  <c:v>68.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>67.7</c:v>
@@ -1663,19 +1663,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>73.40000000000001</c:v>
+                  <c:v>73.3</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>72.90000000000001</c:v>
+                  <c:v>72.8</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>72.40000000000001</c:v>
+                  <c:v>72.3</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>71.8</c:v>
+                  <c:v>71.90000000000001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>71.3</c:v>
+                  <c:v>71.40000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>70.90000000000001</c:v>
@@ -1687,34 +1687,34 @@
                   <c:v>69.8</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>69.2</c:v>
+                  <c:v>69.3</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>68.8</c:v>
+                  <c:v>68.7</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>68.3</c:v>
+                  <c:v>68.2</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>67.7</c:v>
+                  <c:v>67.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>67.2</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>66.5</c:v>
+                  <c:v>66.7</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>66.3</c:v>
+                  <c:v>66.2</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>65.5</c:v>
+                  <c:v>65.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>65</c:v>
+                  <c:v>65.09999999999999</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>64.5</c:v>
+                  <c:v>64.59999999999999</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>64</c:v>
@@ -1882,7 +1882,7 @@
                   <c:v>50123</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>41872</c:v>
+                  <c:v>41693</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>39931</c:v>
@@ -1900,7 +1900,7 @@
                   <c:v>12074</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3031</c:v>
+                  <c:v>3046</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>2912</c:v>
@@ -2734,7 +2734,7 @@
         <v>23480008</v>
       </c>
       <c r="H7" s="10">
-        <v>53730132</v>
+        <v>53758718</v>
       </c>
       <c r="I7" s="10">
         <v>3399</v>
@@ -2763,13 +2763,13 @@
         <v>10132364</v>
       </c>
       <c r="H8" s="10">
-        <v>21510587</v>
+        <v>21588217</v>
       </c>
       <c r="I8" s="10">
         <v>3634</v>
       </c>
       <c r="J8" s="11">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="9" spans="2:10">
@@ -2792,13 +2792,13 @@
         <v>40290893</v>
       </c>
       <c r="H9" s="10">
-        <v>81150680</v>
+        <v>81337339</v>
       </c>
       <c r="I9" s="10">
         <v>3865</v>
       </c>
       <c r="J9" s="11">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="10" spans="2:10">
@@ -2821,13 +2821,13 @@
         <v>47057019</v>
       </c>
       <c r="H10" s="10">
-        <v>91467771</v>
+        <v>91030563</v>
       </c>
       <c r="I10" s="10">
         <v>3991</v>
       </c>
       <c r="J10" s="11">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="11" spans="2:10">
@@ -2850,7 +2850,7 @@
         <v>93212292</v>
       </c>
       <c r="H11" s="10">
-        <v>172488260</v>
+        <v>172236284</v>
       </c>
       <c r="I11" s="10">
         <v>4199</v>
@@ -2879,13 +2879,13 @@
         <v>47134953</v>
       </c>
       <c r="H12" s="10">
-        <v>85814677</v>
+        <v>86429807</v>
       </c>
       <c r="I12" s="10">
         <v>4206</v>
       </c>
       <c r="J12" s="11">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="13" spans="2:10">
@@ -2908,13 +2908,13 @@
         <v>10717004</v>
       </c>
       <c r="H13" s="10">
-        <v>19078435</v>
+        <v>19005147</v>
       </c>
       <c r="I13" s="10">
         <v>4278</v>
       </c>
       <c r="J13" s="11">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="14" spans="2:10">
@@ -2937,13 +2937,13 @@
         <v>31979604</v>
       </c>
       <c r="H14" s="10">
-        <v>56145545</v>
+        <v>55838981</v>
       </c>
       <c r="I14" s="10">
         <v>4475</v>
       </c>
       <c r="J14" s="11">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="15" spans="2:10">
@@ -2966,7 +2966,7 @@
         <v>125777558</v>
       </c>
       <c r="H15" s="10">
-        <v>212186141</v>
+        <v>212741313</v>
       </c>
       <c r="I15" s="10">
         <v>4552</v>
@@ -2980,28 +2980,28 @@
         <v>44</v>
       </c>
       <c r="C16" s="8">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="D16" s="8">
-        <v>165882</v>
+        <v>25996</v>
       </c>
       <c r="E16" s="8">
-        <v>30947</v>
+        <v>4972</v>
       </c>
       <c r="F16" s="8">
-        <v>7247</v>
+        <v>1188</v>
       </c>
       <c r="G16" s="10">
-        <v>36119539</v>
+        <v>6093759</v>
       </c>
       <c r="H16" s="10">
-        <v>55853659</v>
+        <v>9529919</v>
       </c>
       <c r="I16" s="10">
-        <v>4984</v>
+        <v>5129</v>
       </c>
       <c r="J16" s="11">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="17" spans="2:10">
@@ -3009,25 +3009,25 @@
         <v>45</v>
       </c>
       <c r="C17" s="8">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D17" s="8">
-        <v>25996</v>
+        <v>165882</v>
       </c>
       <c r="E17" s="8">
-        <v>4972</v>
+        <v>30947</v>
       </c>
       <c r="F17" s="8">
-        <v>1188</v>
+        <v>7247</v>
       </c>
       <c r="G17" s="10">
-        <v>6093759</v>
+        <v>36119539</v>
       </c>
       <c r="H17" s="10">
-        <v>9448527</v>
+        <v>55858249</v>
       </c>
       <c r="I17" s="10">
-        <v>5129</v>
+        <v>4984</v>
       </c>
       <c r="J17" s="11">
         <v>1.55</v>
@@ -3111,10 +3111,10 @@
         <v>3721</v>
       </c>
       <c r="H7" s="11">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="I7" s="10">
-        <v>41471297</v>
+        <v>41480838</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -3137,10 +3137,10 @@
         <v>3687</v>
       </c>
       <c r="H8" s="11">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="I8" s="10">
-        <v>50190233</v>
+        <v>50426592</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -3163,10 +3163,10 @@
         <v>3680</v>
       </c>
       <c r="H9" s="11">
-        <v>15.1</v>
+        <v>15.3</v>
       </c>
       <c r="I9" s="10">
-        <v>50174573</v>
+        <v>49848766</v>
       </c>
     </row>
     <row r="10" spans="2:9">
@@ -3189,10 +3189,10 @@
         <v>3666</v>
       </c>
       <c r="H10" s="11">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="I10" s="10">
-        <v>40509820</v>
+        <v>40697765</v>
       </c>
     </row>
     <row r="11" spans="2:9">
@@ -3215,10 +3215,10 @@
         <v>3653</v>
       </c>
       <c r="H11" s="11">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="I11" s="10">
-        <v>109521849</v>
+        <v>109341735</v>
       </c>
     </row>
     <row r="12" spans="2:9">
@@ -3281,10 +3281,10 @@
         <v>3643</v>
       </c>
       <c r="H14" s="11">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="I14" s="10">
-        <v>40561043</v>
+        <v>40630757</v>
       </c>
     </row>
     <row r="15" spans="2:9">
@@ -3310,7 +3310,7 @@
         <v>14.9</v>
       </c>
       <c r="I15" s="10">
-        <v>40330524</v>
+        <v>40585352</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -3333,10 +3333,10 @@
         <v>3621</v>
       </c>
       <c r="H16" s="11">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="I16" s="10">
-        <v>80305396</v>
+        <v>80324634</v>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -3359,10 +3359,10 @@
         <v>3617</v>
       </c>
       <c r="H17" s="11">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="I17" s="10">
-        <v>49464237</v>
+        <v>49158813</v>
       </c>
     </row>
     <row r="18" spans="2:9">
@@ -3385,10 +3385,10 @@
         <v>3614</v>
       </c>
       <c r="H18" s="11">
-        <v>15.1</v>
+        <v>14.8</v>
       </c>
       <c r="I18" s="10">
-        <v>40223978</v>
+        <v>40340020</v>
       </c>
     </row>
     <row r="19" spans="2:9">
@@ -3414,7 +3414,7 @@
         <v>14.8</v>
       </c>
       <c r="I19" s="10">
-        <v>14587230</v>
+        <v>14636122</v>
       </c>
     </row>
     <row r="20" spans="2:9">
@@ -3437,10 +3437,10 @@
         <v>3607</v>
       </c>
       <c r="H20" s="11">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="I20" s="10">
-        <v>80576937</v>
+        <v>80377059</v>
       </c>
     </row>
     <row r="21" spans="2:9">
@@ -3503,10 +3503,10 @@
         <v>3598</v>
       </c>
       <c r="H23" s="11">
-        <v>14.7</v>
+        <v>15</v>
       </c>
       <c r="I23" s="10">
-        <v>26796848</v>
+        <v>26665814</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -3572,7 +3572,7 @@
         <v>15.1</v>
       </c>
       <c r="I26" s="10">
-        <v>79889178</v>
+        <v>79463550</v>
       </c>
     </row>
     <row r="27" spans="2:9">
@@ -3655,10 +3655,10 @@
         <v>3573</v>
       </c>
       <c r="H30" s="11">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="I30" s="10">
-        <v>43834999</v>
+        <v>43823750</v>
       </c>
     </row>
     <row r="31" spans="2:9">
@@ -3681,10 +3681,10 @@
         <v>3567</v>
       </c>
       <c r="H31" s="11">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="I31" s="10">
-        <v>39859386</v>
+        <v>39533803</v>
       </c>
     </row>
     <row r="32" spans="2:9">
@@ -3710,7 +3710,7 @@
         <v>15</v>
       </c>
       <c r="I32" s="10">
-        <v>43852272</v>
+        <v>43659853</v>
       </c>
     </row>
     <row r="33" spans="2:9">
@@ -3884,7 +3884,7 @@
         <v>168157</v>
       </c>
       <c r="D7" s="8">
-        <v>12356</v>
+        <v>12359</v>
       </c>
       <c r="E7" s="11">
         <v>7.3</v>
@@ -3893,7 +3893,7 @@
         <v>83.09999999999999</v>
       </c>
       <c r="G7" s="11">
-        <v>73.40000000000001</v>
+        <v>73.3</v>
       </c>
     </row>
     <row r="8" spans="2:7">
@@ -3904,16 +3904,16 @@
         <v>168157</v>
       </c>
       <c r="D8" s="8">
-        <v>13209</v>
+        <v>13444</v>
       </c>
       <c r="E8" s="11">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="11">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="G8" s="11">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="9" spans="2:7">
@@ -3924,7 +3924,7 @@
         <v>168157</v>
       </c>
       <c r="D9" s="8">
-        <v>14532</v>
+        <v>14470</v>
       </c>
       <c r="E9" s="11">
         <v>8.6</v>
@@ -3933,7 +3933,7 @@
         <v>81.5</v>
       </c>
       <c r="G9" s="11">
-        <v>72.40000000000001</v>
+        <v>72.3</v>
       </c>
     </row>
     <row r="10" spans="2:7">
@@ -3944,16 +3944,16 @@
         <v>168157</v>
       </c>
       <c r="D10" s="8">
-        <v>15822</v>
+        <v>15692</v>
       </c>
       <c r="E10" s="11">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F10" s="11">
-        <v>80.7</v>
+        <v>80.8</v>
       </c>
       <c r="G10" s="11">
-        <v>71.8</v>
+        <v>71.90000000000001</v>
       </c>
     </row>
     <row r="11" spans="2:7">
@@ -3964,16 +3964,16 @@
         <v>168157</v>
       </c>
       <c r="D11" s="8">
-        <v>17156</v>
+        <v>17124</v>
       </c>
       <c r="E11" s="11">
         <v>10.2</v>
       </c>
       <c r="F11" s="11">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="G11" s="11">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="12" spans="2:7">
@@ -3984,13 +3984,13 @@
         <v>168157</v>
       </c>
       <c r="D12" s="8">
-        <v>18414</v>
+        <v>18382</v>
       </c>
       <c r="E12" s="11">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="F12" s="11">
-        <v>79</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="G12" s="11">
         <v>70.90000000000001</v>
@@ -4001,10 +4001,10 @@
         <v>7</v>
       </c>
       <c r="C13" s="8">
-        <v>156295</v>
+        <v>156078</v>
       </c>
       <c r="D13" s="8">
-        <v>18463</v>
+        <v>18441</v>
       </c>
       <c r="E13" s="11">
         <v>11.8</v>
@@ -4021,13 +4021,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="8">
-        <v>144330</v>
+        <v>144020</v>
       </c>
       <c r="D14" s="8">
-        <v>18662</v>
+        <v>18676</v>
       </c>
       <c r="E14" s="11">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="F14" s="11">
         <v>77.3</v>
@@ -4041,19 +4041,19 @@
         <v>9</v>
       </c>
       <c r="C15" s="8">
-        <v>132333</v>
+        <v>132098</v>
       </c>
       <c r="D15" s="8">
-        <v>18431</v>
+        <v>18288</v>
       </c>
       <c r="E15" s="11">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
       <c r="F15" s="11">
         <v>76.5</v>
       </c>
       <c r="G15" s="11">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="16" spans="2:7">
@@ -4061,19 +4061,19 @@
         <v>10</v>
       </c>
       <c r="C16" s="8">
-        <v>120413</v>
+        <v>120031</v>
       </c>
       <c r="D16" s="8">
-        <v>18023</v>
+        <v>18353</v>
       </c>
       <c r="E16" s="11">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="F16" s="11">
         <v>75.59999999999999</v>
       </c>
       <c r="G16" s="11">
-        <v>68.8</v>
+        <v>68.7</v>
       </c>
     </row>
     <row r="17" spans="2:7">
@@ -4081,19 +4081,19 @@
         <v>11</v>
       </c>
       <c r="C17" s="8">
-        <v>108562</v>
+        <v>107906</v>
       </c>
       <c r="D17" s="8">
-        <v>17455</v>
+        <v>17452</v>
       </c>
       <c r="E17" s="11">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="F17" s="11">
         <v>74.8</v>
       </c>
       <c r="G17" s="11">
-        <v>68.3</v>
+        <v>68.2</v>
       </c>
     </row>
     <row r="18" spans="2:7">
@@ -4101,10 +4101,10 @@
         <v>12</v>
       </c>
       <c r="C18" s="8">
-        <v>96432</v>
+        <v>95862</v>
       </c>
       <c r="D18" s="8">
-        <v>16929</v>
+        <v>16852</v>
       </c>
       <c r="E18" s="11">
         <v>17.6</v>
@@ -4113,7 +4113,7 @@
         <v>73.90000000000001</v>
       </c>
       <c r="G18" s="11">
-        <v>67.7</v>
+        <v>67.59999999999999</v>
       </c>
     </row>
     <row r="19" spans="2:7">
@@ -4121,13 +4121,13 @@
         <v>13</v>
       </c>
       <c r="C19" s="8">
-        <v>84471</v>
+        <v>83978</v>
       </c>
       <c r="D19" s="8">
-        <v>15746</v>
+        <v>15720</v>
       </c>
       <c r="E19" s="11">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="F19" s="11">
         <v>73</v>
@@ -4141,19 +4141,19 @@
         <v>14</v>
       </c>
       <c r="C20" s="8">
-        <v>72614</v>
+        <v>72025</v>
       </c>
       <c r="D20" s="8">
-        <v>14858</v>
+        <v>14299</v>
       </c>
       <c r="E20" s="11">
-        <v>20.5</v>
+        <v>19.9</v>
       </c>
       <c r="F20" s="11">
-        <v>72</v>
+        <v>72.2</v>
       </c>
       <c r="G20" s="11">
-        <v>66.5</v>
+        <v>66.7</v>
       </c>
     </row>
     <row r="21" spans="2:7">
@@ -4161,19 +4161,19 @@
         <v>15</v>
       </c>
       <c r="C21" s="8">
-        <v>60678</v>
+        <v>60079</v>
       </c>
       <c r="D21" s="8">
-        <v>12895</v>
+        <v>12933</v>
       </c>
       <c r="E21" s="11">
-        <v>21.3</v>
+        <v>21.5</v>
       </c>
       <c r="F21" s="11">
-        <v>71.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="G21" s="11">
-        <v>66.3</v>
+        <v>66.2</v>
       </c>
     </row>
     <row r="22" spans="2:7">
@@ -4181,19 +4181,19 @@
         <v>16</v>
       </c>
       <c r="C22" s="8">
-        <v>48566</v>
+        <v>48096</v>
       </c>
       <c r="D22" s="8">
-        <v>11454</v>
+        <v>11063</v>
       </c>
       <c r="E22" s="11">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="F22" s="11">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="G22" s="11">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
     </row>
     <row r="23" spans="2:7">
@@ -4201,19 +4201,19 @@
         <v>17</v>
       </c>
       <c r="C23" s="8">
-        <v>36484</v>
+        <v>36117</v>
       </c>
       <c r="D23" s="8">
-        <v>8991</v>
+        <v>8778</v>
       </c>
       <c r="E23" s="11">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="F23" s="11">
-        <v>69.5</v>
+        <v>69.7</v>
       </c>
       <c r="G23" s="11">
-        <v>65</v>
+        <v>65.09999999999999</v>
       </c>
     </row>
     <row r="24" spans="2:7">
@@ -4221,19 +4221,19 @@
         <v>18</v>
       </c>
       <c r="C24" s="8">
-        <v>24243</v>
+        <v>23919</v>
       </c>
       <c r="D24" s="8">
-        <v>6496</v>
+        <v>6292</v>
       </c>
       <c r="E24" s="11">
-        <v>26.8</v>
+        <v>26.3</v>
       </c>
       <c r="F24" s="11">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G24" s="11">
-        <v>64.5</v>
+        <v>64.59999999999999</v>
       </c>
     </row>
     <row r="25" spans="2:7">
@@ -4241,13 +4241,13 @@
         <v>19</v>
       </c>
       <c r="C25" s="8">
-        <v>11996</v>
+        <v>11902</v>
       </c>
       <c r="D25" s="8">
-        <v>3360</v>
+        <v>3429</v>
       </c>
       <c r="E25" s="11">
-        <v>28</v>
+        <v>28.8</v>
       </c>
       <c r="F25" s="11">
         <v>67.7</v>
@@ -4323,7 +4323,7 @@
         <v>108</v>
       </c>
       <c r="I7" s="8">
-        <v>41872</v>
+        <v>41693</v>
       </c>
     </row>
     <row r="8" spans="2:9">
@@ -4343,7 +4343,7 @@
         <v>124</v>
       </c>
       <c r="I8" s="8">
-        <v>3863</v>
+        <v>3855</v>
       </c>
     </row>
     <row r="9" spans="2:9">
@@ -4357,7 +4357,7 @@
         <v>109</v>
       </c>
       <c r="E9" s="8">
-        <v>41872</v>
+        <v>41693</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>131</v>
@@ -4477,13 +4477,13 @@
         <v>122</v>
       </c>
       <c r="E15" s="8">
-        <v>3031</v>
+        <v>3046</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>121</v>
       </c>
       <c r="I15" s="8">
-        <v>5082</v>
+        <v>5093</v>
       </c>
     </row>
     <row r="16" spans="2:9">
@@ -4503,7 +4503,7 @@
         <v>114</v>
       </c>
       <c r="I16" s="8">
-        <v>144955</v>
+        <v>144685</v>
       </c>
     </row>
     <row r="17" spans="2:9">

--- a/reporting/RedAndYellow_Analytics.xlsx
+++ b/reporting/RedAndYellow_Analytics.xlsx
@@ -199,13 +199,13 @@
     <t>Certificate</t>
   </si>
   <si>
+    <t>Copywriting</t>
+  </si>
+  <si>
     <t>Higher Certificate in Marketing and Branding</t>
   </si>
   <si>
     <t>On-campus</t>
-  </si>
-  <si>
-    <t>Copywriting</t>
   </si>
   <si>
     <t>Project Management</t>
@@ -6537,46 +6537,46 @@
         <v>58</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="10"/>
+        <v>55</v>
+      </c>
+      <c r="E9" s="10">
+        <v>13500</v>
+      </c>
       <c r="F9" s="8">
-        <v>15818</v>
+        <v>15796</v>
       </c>
       <c r="G9" s="8">
         <v>6586</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="10"/>
+      <c r="H9" s="11">
+        <v>14.8</v>
+      </c>
+      <c r="I9" s="10">
+        <v>73640481</v>
+      </c>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="10">
-        <v>13500</v>
-      </c>
+      <c r="E10" s="10"/>
       <c r="F10" s="8">
-        <v>15796</v>
+        <v>15818</v>
       </c>
       <c r="G10" s="8">
         <v>6586</v>
       </c>
-      <c r="H10" s="11">
-        <v>14.8</v>
-      </c>
-      <c r="I10" s="10">
-        <v>73640481</v>
-      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="10"/>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="7" t="s">
@@ -6606,7 +6606,7 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>57</v>
@@ -6632,7 +6632,7 @@
         <v>57</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="8">
@@ -6802,7 +6802,7 @@
         <v>65</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="8">
@@ -6900,7 +6900,7 @@
         <v>65</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" s="10"/>
       <c r="F24" s="8">
@@ -7176,7 +7176,7 @@
         <v>57</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="8">
@@ -14942,7 +14942,7 @@
         <v>1255</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>1239</v>
@@ -14969,7 +14969,7 @@
         <v>1255</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>1239</v>
@@ -14996,7 +14996,7 @@
         <v>1255</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>1239</v>
@@ -15075,7 +15075,7 @@
         <v>65</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>1239</v>
@@ -15102,7 +15102,7 @@
         <v>1262</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>1239</v>
@@ -15129,7 +15129,7 @@
         <v>1262</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>1239</v>
@@ -15206,7 +15206,7 @@
         <v>1262</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>1239</v>
@@ -15285,7 +15285,7 @@
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>54</v>
@@ -15778,7 +15778,7 @@
         <v>57</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>1239</v>
@@ -15832,7 +15832,7 @@
         <v>57</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>1239</v>
@@ -15859,7 +15859,7 @@
         <v>57</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>1239</v>
@@ -15880,13 +15880,13 @@
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>57</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>1239</v>
@@ -15907,7 +15907,7 @@
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>57</v>
@@ -15967,7 +15967,7 @@
         <v>57</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>1239</v>
@@ -16527,7 +16527,7 @@
         <v>65</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>1239</v>
@@ -16554,7 +16554,7 @@
         <v>65</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>1239</v>
@@ -16581,7 +16581,7 @@
         <v>65</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>1239</v>

--- a/reporting/RedAndYellow_Analytics.xlsx
+++ b/reporting/RedAndYellow_Analytics.xlsx
@@ -31,7 +31,7 @@
     <t>CRM &amp; Academic Analytics - marketing spend through to student outcomes</t>
   </si>
   <si>
-    <t>Generated 09 September 2026 from the dbt warehouse. Catalogue is real; all people and campaigns are synthetic.</t>
+    <t>Generated 10 September 2026 from the dbt warehouse. Catalogue is real; all people and campaigns are synthetic.</t>
   </si>
   <si>
     <t>1,500,000</t>
@@ -250,13 +250,13 @@
     <t>Postgraduate Diploma in Digital Marketing</t>
   </si>
   <si>
+    <t>Data Analysis</t>
+  </si>
+  <si>
     <t>Strategic Foresight for Leaders</t>
   </si>
   <si>
     <t>Executive education</t>
-  </si>
-  <si>
-    <t>Data Analysis</t>
   </si>
   <si>
     <t>Sports Sponsorship Marketing</t>
@@ -4009,14 +4009,14 @@
     <font>
       <b/>
       <sz val="22"/>
-      <color rgb="FF22252A"/>
+      <color rgb="FF1D1D1B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF5A6472"/>
+      <color rgb="FF60646B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4024,14 +4024,14 @@
     <font>
       <b/>
       <sz val="26"/>
-      <color rgb="FFE03127"/>
+      <color rgb="FFF52635"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF5A6472"/>
+      <color rgb="FF60646B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4039,7 +4039,7 @@
     <font>
       <b/>
       <sz val="13"/>
-      <color rgb="FF22252A"/>
+      <color rgb="FFF52635"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -4055,20 +4055,20 @@
     <font>
       <i/>
       <sz val="10"/>
-      <color rgb="FF5A6472"/>
+      <color rgb="FF60646B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF22252A"/>
+      <color rgb="FF1D1D1B"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4077,13 +4077,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF22252A"/>
+        <fgColor rgb="FF1D1D1B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF6D6"/>
+        <fgColor rgb="FFFFF9F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF3D6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4100,23 +4106,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FFD8DDE4"/>
+      <bottom style="medium">
+        <color rgb="FFFFB71B"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF22252A"/>
+        <color rgb="FF1D1D1B"/>
       </left>
       <right style="thin">
-        <color rgb="FF22252A"/>
+        <color rgb="FF1D1D1B"/>
       </right>
       <top style="thin">
-        <color rgb="FF22252A"/>
+        <color rgb="FF1D1D1B"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF22252A"/>
+        <color rgb="FF1D1D1B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4137,16 +4143,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFC629"/>
+        <color rgb="FFFFB71B"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFC629"/>
+        <color rgb="FFFFB71B"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFC629"/>
+        <color rgb="FFFFB71B"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFFFC629"/>
+        <color rgb="FFFFB71B"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4170,13 +4176,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4247,7 +4253,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="E03127"/>
+              <a:srgbClr val="F52635"/>
             </a:solidFill>
           </c:spPr>
           <c:cat>
@@ -4374,7 +4380,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="2E6E8E"/>
+              <a:srgbClr val="007C83"/>
             </a:solidFill>
           </c:spPr>
           <c:cat>
@@ -4537,7 +4543,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="4C9F70"/>
+              <a:srgbClr val="008C45"/>
             </a:solidFill>
           </c:spPr>
           <c:cat>
@@ -4700,7 +4706,7 @@
           <c:spPr>
             <a:ln w="28575">
               <a:solidFill>
-                <a:srgbClr val="E03127"/>
+                <a:srgbClr val="F52635"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -4849,7 +4855,7 @@
           <c:spPr>
             <a:ln w="28575">
               <a:solidFill>
-                <a:srgbClr val="F0A202"/>
+                <a:srgbClr val="E39B16"/>
               </a:solidFill>
             </a:ln>
           </c:spPr>
@@ -5088,7 +5094,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="C7522A"/>
+              <a:srgbClr val="D9574A"/>
             </a:solidFill>
           </c:spPr>
           <c:cat>
@@ -6976,51 +6982,51 @@
         <v>75</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E26" s="10">
-        <v>27000</v>
+        <v>13500</v>
       </c>
       <c r="F26" s="8">
-        <v>15963</v>
+        <v>15801</v>
       </c>
       <c r="G26" s="8">
         <v>6474</v>
       </c>
       <c r="H26" s="12">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="I26" s="10">
-        <v>143879154</v>
+        <v>71780786</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="7" t="s">
         <v>77</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>54</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="10">
-        <v>13500</v>
+        <v>27000</v>
       </c>
       <c r="F27" s="8">
-        <v>15801</v>
+        <v>15963</v>
       </c>
       <c r="G27" s="8">
         <v>6474</v>
       </c>
       <c r="H27" s="12">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="I27" s="10">
-        <v>71780786</v>
+        <v>143879154</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -14723,7 +14729,7 @@
         <v>1243</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>55</v>
@@ -15275,7 +15281,7 @@
         <v>1267</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>55</v>
@@ -15446,7 +15452,7 @@
     </row>
     <row r="34" spans="2:10">
       <c r="B34" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>54</v>
@@ -16094,7 +16100,7 @@
         <v>1282</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>55</v>
@@ -16791,7 +16797,7 @@
         <v>1297</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>55</v>
@@ -17045,10 +17051,10 @@
     </row>
     <row r="91" spans="2:10">
       <c r="B91" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>55</v>

--- a/reporting/RedAndYellow_Analytics.xlsx
+++ b/reporting/RedAndYellow_Analytics.xlsx
@@ -199,15 +199,15 @@
     <t>Certificate</t>
   </si>
   <si>
+    <t>Higher Certificate in Marketing and Branding</t>
+  </si>
+  <si>
+    <t>On-campus</t>
+  </si>
+  <si>
     <t>Copywriting</t>
   </si>
   <si>
-    <t>Higher Certificate in Marketing and Branding</t>
-  </si>
-  <si>
-    <t>On-campus</t>
-  </si>
-  <si>
     <t>Project Management</t>
   </si>
   <si>
@@ -244,19 +244,19 @@
     <t>Creative Thinking</t>
   </si>
   <si>
+    <t>Postgraduate Diploma in Digital Marketing</t>
+  </si>
+  <si>
     <t>Digital Content &amp; Copywriting</t>
   </si>
   <si>
-    <t>Postgraduate Diploma in Digital Marketing</t>
+    <t>Strategic Foresight for Leaders</t>
+  </si>
+  <si>
+    <t>Executive education</t>
   </si>
   <si>
     <t>Data Analysis</t>
-  </si>
-  <si>
-    <t>Strategic Foresight for Leaders</t>
-  </si>
-  <si>
-    <t>Executive education</t>
   </si>
   <si>
     <t>Sports Sponsorship Marketing</t>
@@ -4068,12 +4068,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7E3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -4094,12 +4100,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE9C46A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE9C46A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE9C46A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE9C46A"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -4164,56 +4185,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFBFBFC"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color rgb="FFD8DDE4"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFD8DDE4"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFD8DDE4"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFD8DDE4"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
@@ -5902,36 +5899,6 @@
     <mergeCell ref="H13:J13"/>
     <mergeCell ref="B24:I26"/>
   </mergeCells>
-  <conditionalFormatting sqref="B11:D13">
-    <cfRule type="notContainsErrors" dxfId="0" priority="4">
-      <formula>NOT(ISERROR(B11))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:D9">
-    <cfRule type="notContainsErrors" dxfId="0" priority="1">
-      <formula>NOT(ISERROR(B7))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E11:G13">
-    <cfRule type="notContainsErrors" dxfId="0" priority="5">
-      <formula>NOT(ISERROR(E11))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:G9">
-    <cfRule type="notContainsErrors" dxfId="0" priority="2">
-      <formula>NOT(ISERROR(E7))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H11:J13">
-    <cfRule type="notContainsErrors" dxfId="0" priority="6">
-      <formula>NOT(ISERROR(H11))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H7:J9">
-    <cfRule type="notContainsErrors" dxfId="0" priority="3">
-      <formula>NOT(ISERROR(H7))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -6576,46 +6543,46 @@
         <v>58</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E9" s="10">
-        <v>13500</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E9" s="10"/>
       <c r="F9" s="8">
-        <v>15796</v>
+        <v>15818</v>
       </c>
       <c r="G9" s="8">
         <v>6586</v>
       </c>
-      <c r="H9" s="12">
-        <v>14.8</v>
-      </c>
-      <c r="I9" s="10">
-        <v>73640481</v>
-      </c>
+      <c r="H9" s="12"/>
+      <c r="I9" s="10"/>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E10" s="10"/>
+        <v>55</v>
+      </c>
+      <c r="E10" s="10">
+        <v>13500</v>
+      </c>
       <c r="F10" s="8">
-        <v>15818</v>
+        <v>15796</v>
       </c>
       <c r="G10" s="8">
         <v>6586</v>
       </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="10"/>
+      <c r="H10" s="12">
+        <v>14.8</v>
+      </c>
+      <c r="I10" s="10">
+        <v>73640481</v>
+      </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" s="7" t="s">
@@ -6645,7 +6612,7 @@
     </row>
     <row r="12" spans="2:9">
       <c r="B12" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>57</v>
@@ -6671,7 +6638,7 @@
         <v>57</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="8">
@@ -6841,7 +6808,7 @@
         <v>65</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="8">
@@ -6936,97 +6903,97 @@
         <v>73</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E24" s="10">
-        <v>14900</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="E24" s="10"/>
       <c r="F24" s="8">
-        <v>15683</v>
+        <v>15650</v>
       </c>
       <c r="G24" s="8">
         <v>6499</v>
       </c>
-      <c r="H24" s="12">
-        <v>15</v>
-      </c>
-      <c r="I24" s="10">
-        <v>79792859</v>
-      </c>
+      <c r="H24" s="12"/>
+      <c r="I24" s="10"/>
     </row>
     <row r="25" spans="2:9">
       <c r="B25" s="7" t="s">
         <v>74</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="10"/>
+        <v>55</v>
+      </c>
+      <c r="E25" s="10">
+        <v>14900</v>
+      </c>
       <c r="F25" s="8">
-        <v>15650</v>
+        <v>15683</v>
       </c>
       <c r="G25" s="8">
         <v>6499</v>
       </c>
-      <c r="H25" s="12"/>
-      <c r="I25" s="10"/>
+      <c r="H25" s="12">
+        <v>15</v>
+      </c>
+      <c r="I25" s="10">
+        <v>79792859</v>
+      </c>
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="7" t="s">
         <v>75</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="D26" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E26" s="10">
-        <v>13500</v>
+        <v>27000</v>
       </c>
       <c r="F26" s="8">
-        <v>15801</v>
+        <v>15963</v>
       </c>
       <c r="G26" s="8">
         <v>6474</v>
       </c>
       <c r="H26" s="12">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="I26" s="10">
-        <v>71780786</v>
+        <v>143879154</v>
       </c>
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="D27" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E27" s="10">
-        <v>27000</v>
+        <v>13500</v>
       </c>
       <c r="F27" s="8">
-        <v>15963</v>
+        <v>15801</v>
       </c>
       <c r="G27" s="8">
         <v>6474</v>
       </c>
       <c r="H27" s="12">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="I27" s="10">
-        <v>143879154</v>
+        <v>71780786</v>
       </c>
     </row>
     <row r="28" spans="2:9">
@@ -7215,7 +7182,7 @@
         <v>57</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E36" s="10"/>
       <c r="F36" s="8">
@@ -14729,7 +14696,7 @@
         <v>1243</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>55</v>
@@ -14993,7 +14960,7 @@
         <v>1256</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>1240</v>
@@ -15020,7 +14987,7 @@
         <v>1256</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>1240</v>
@@ -15047,7 +15014,7 @@
         <v>1256</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>1240</v>
@@ -15126,7 +15093,7 @@
         <v>65</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>1240</v>
@@ -15153,7 +15120,7 @@
         <v>1263</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>1240</v>
@@ -15180,7 +15147,7 @@
         <v>1263</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>1240</v>
@@ -15257,7 +15224,7 @@
         <v>1263</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>1240</v>
@@ -15281,7 +15248,7 @@
         <v>1267</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>55</v>
@@ -15336,7 +15303,7 @@
     </row>
     <row r="30" spans="2:10">
       <c r="B30" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>54</v>
@@ -15452,7 +15419,7 @@
     </row>
     <row r="34" spans="2:10">
       <c r="B34" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>54</v>
@@ -15622,7 +15589,7 @@
     </row>
     <row r="40" spans="2:10">
       <c r="B40" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C40" s="7" t="s">
         <v>54</v>
@@ -15829,7 +15796,7 @@
         <v>57</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>1240</v>
@@ -15883,7 +15850,7 @@
         <v>57</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>1240</v>
@@ -15910,7 +15877,7 @@
         <v>57</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>1240</v>
@@ -15931,13 +15898,13 @@
     </row>
     <row r="51" spans="2:10">
       <c r="B51" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>57</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E51" s="7" t="s">
         <v>1240</v>
@@ -15958,7 +15925,7 @@
     </row>
     <row r="52" spans="2:10">
       <c r="B52" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>57</v>
@@ -16018,7 +15985,7 @@
         <v>57</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>1240</v>
@@ -16100,7 +16067,7 @@
         <v>1282</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D57" s="7" t="s">
         <v>55</v>
@@ -16572,13 +16539,13 @@
     </row>
     <row r="74" spans="2:10">
       <c r="B74" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>1240</v>
@@ -16605,7 +16572,7 @@
         <v>65</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>1240</v>
@@ -16632,7 +16599,7 @@
         <v>65</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>1240</v>
@@ -16797,7 +16764,7 @@
         <v>1297</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D82" s="7" t="s">
         <v>55</v>
@@ -17051,10 +17018,10 @@
     </row>
     <row r="91" spans="2:10">
       <c r="B91" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C91" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="D91" s="7" t="s">
         <v>55</v>

--- a/reporting/RedAndYellow_Analytics.xlsx
+++ b/reporting/RedAndYellow_Analytics.xlsx
@@ -15,15 +15,16 @@
     <sheet name="DQ Scorecard" sheetId="6" r:id="rId6"/>
     <sheet name="Salesforce CRM" sheetId="7" r:id="rId7"/>
     <sheet name="Predictive Models" sheetId="8" r:id="rId8"/>
-    <sheet name="Catalogue" sheetId="9" r:id="rId9"/>
-    <sheet name="Method &amp; Caveats" sheetId="10" r:id="rId10"/>
+    <sheet name="Recommendations" sheetId="9" r:id="rId9"/>
+    <sheet name="Catalogue" sheetId="10" r:id="rId10"/>
+    <sheet name="Method &amp; Caveats" sheetId="11" r:id="rId11"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2651" uniqueCount="1321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2696" uniqueCount="1362">
   <si>
     <t>Red &amp; Yellow</t>
   </si>
@@ -229,18 +230,18 @@
     <t>Graphic Design Intermediate with Adobe Photoshop</t>
   </si>
   <si>
+    <t>Part-Time Higher Certificate in Graphic Design</t>
+  </si>
+  <si>
+    <t>Part-Time Postgraduate Diploma in Digital Marketing</t>
+  </si>
+  <si>
+    <t>Postgraduate programme</t>
+  </si>
+  <si>
     <t>Part-Time Higher Certificate in Business Management</t>
   </si>
   <si>
-    <t>Part-Time Higher Certificate in Graphic Design</t>
-  </si>
-  <si>
-    <t>Part-Time Postgraduate Diploma in Digital Marketing</t>
-  </si>
-  <si>
-    <t>Postgraduate programme</t>
-  </si>
-  <si>
     <t>Shopper Marketing</t>
   </si>
   <si>
@@ -3716,6 +3717,129 @@
   </si>
   <si>
     <t>An AUC in the mid-0.6s is the honest result for human decisions with this much unexplained variation. A model claiming 0.95 here would mean a feature had leaked. The lift is the number to act on.</t>
+  </si>
+  <si>
+    <t>Recommendations and solutions</t>
+  </si>
+  <si>
+    <t>An action register linked to the report signals, owners and measurable outcomes.</t>
+  </si>
+  <si>
+    <t>signal</t>
+  </si>
+  <si>
+    <t>solution</t>
+  </si>
+  <si>
+    <t>owner</t>
+  </si>
+  <si>
+    <t>success measure</t>
+  </si>
+  <si>
+    <t>Acquisition</t>
+  </si>
+  <si>
+    <t>Channel response, enrolment rate and revenue per member diverge.</t>
+  </si>
+  <si>
+    <t>Test budget toward the strongest channel and set a stop rule for spend without response.</t>
+  </si>
+  <si>
+    <t>ROAS, spend per response and revenue per member</t>
+  </si>
+  <si>
+    <t>Admissions</t>
+  </si>
+  <si>
+    <t>Priority propensity leads convert at a higher rate.</t>
+  </si>
+  <si>
+    <t>Route Priority leads to a human queue within 24 hours; automate Low-band nurture.</t>
+  </si>
+  <si>
+    <t>Response SLA, conversion rate and top-band lift</t>
+  </si>
+  <si>
+    <t>Student success</t>
+  </si>
+  <si>
+    <t>Attendance below 65% in month one predicts higher withdrawal.</t>
+  </si>
+  <si>
+    <t>Trigger a week-4 support conversation and log the intervention.</t>
+  </si>
+  <si>
+    <t>Week-4 attendance and withdrawal rate</t>
+  </si>
+  <si>
+    <t>CRM quality</t>
+  </si>
+  <si>
+    <t>Blank-only filters, duplicates and missing contact fields weaken follow-up.</t>
+  </si>
+  <si>
+    <t>Require external IDs, email and campaign membership; queue exceptions daily.</t>
+  </si>
+  <si>
+    <t>CRM + Data</t>
+  </si>
+  <si>
+    <t>Email completeness, duplicate rate and issue SLA</t>
+  </si>
+  <si>
+    <t>Catalogue</t>
+  </si>
+  <si>
+    <t>Enquire-for-price offerings have no defensible numeric fee.</t>
+  </si>
+  <si>
+    <t>Keep fee null with a price status; add values only from verified source evidence.</t>
+  </si>
+  <si>
+    <t>Data stewardship</t>
+  </si>
+  <si>
+    <t>No unknown price reported as zero</t>
+  </si>
+  <si>
+    <t>Platform</t>
+  </si>
+  <si>
+    <t>Fabric silver/gold and GA4 remain gated by external execution.</t>
+  </si>
+  <si>
+    <t>Fix T-SQL compatibility, rerun dbt in Fabric, then add GA4 as dated bronze.</t>
+  </si>
+  <si>
+    <t>Data engineering</t>
+  </si>
+  <si>
+    <t>Passing Fabric run and reconciled GA4 mart</t>
+  </si>
+  <si>
+    <t>90-day rollout</t>
+  </si>
+  <si>
+    <t>Days 0-30 - Stabilise</t>
+  </si>
+  <si>
+    <t>Confirm field rules, remove blank-bound slicers, assign the Priority queue and baseline KPI cards.</t>
+  </si>
+  <si>
+    <t>Days 31-60 - Test</t>
+  </si>
+  <si>
+    <t>Run channel and follow-up holdouts, log student-support interventions and keep cohort definitions fixed.</t>
+  </si>
+  <si>
+    <t>Days 61-90 - Scale</t>
+  </si>
+  <si>
+    <t>Promote only interventions that beat baseline and monitor model drift by delivery mode and channel.</t>
+  </si>
+  <si>
+    <t>Model scores order a human worklist; they must never make an automated adverse decision.</t>
   </si>
   <si>
     <t>Programme catalogue (real)</t>
@@ -5906,6 +6030,2572 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:J95"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" customWidth="1"/>
+    <col min="2" max="2" width="52.7109375" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" customWidth="1"/>
+    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17.7109375" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="21.7109375" customWidth="1"/>
+    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="21.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10">
+      <c r="B2" s="1" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10">
+      <c r="B3" s="2" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" ht="30" customHeight="1">
+      <c r="B6" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>1275</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>1276</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="B7" s="7" t="s">
+        <v>1279</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F7" s="8">
+        <v>1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="B8" s="7" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F8" s="8">
+        <v>7</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H8" s="10">
+        <v>27000</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="B9" s="7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F9" s="8">
+        <v>2</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
+      <c r="B10" s="7" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F11" s="8">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H11" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F12" s="8">
+        <v>2</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
+      <c r="B13" s="7" t="s">
+        <v>1292</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F13" s="8">
+        <v>2</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H13" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10">
+      <c r="B14" s="7" t="s">
+        <v>1293</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F14" s="8">
+        <v>2</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H14" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J14" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="7" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F15" s="8">
+        <v>2</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10">
+      <c r="B16" s="7" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F16" s="8">
+        <v>13</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H16" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J16" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17" s="7" t="s">
+        <v>1296</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F17" s="8">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18" s="7" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H18" s="10"/>
+      <c r="I18" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J18" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19" s="7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F19" s="8">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H19" s="10"/>
+      <c r="I19" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20" s="7" t="s">
+        <v>1300</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F20" s="8">
+        <v>11</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H20" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J20" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21" s="7" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22" s="7" t="s">
+        <v>1301</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F22" s="8">
+        <v>1</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J22" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23" s="7" t="s">
+        <v>1303</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F23" s="8">
+        <v>3</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H23" s="10"/>
+      <c r="I23" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J23" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24" s="7" t="s">
+        <v>1305</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F24" s="8">
+        <v>3</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J24" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25" s="7" t="s">
+        <v>1306</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F25" s="8"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J25" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F26" s="8">
+        <v>3</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H26" s="10"/>
+      <c r="I26" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J26" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27" s="7" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F27" s="8">
+        <v>3</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J27" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28" s="7" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F28" s="8">
+        <v>7</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H28" s="10">
+        <v>27000</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J28" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29" s="7" t="s">
+        <v>1309</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F29" s="8">
+        <v>14</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H29" s="10">
+        <v>14900</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J29" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30" s="7" t="s">
+        <v>1310</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F30" s="8">
+        <v>11</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H30" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I30" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J30" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F31" s="8">
+        <v>7</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H31" s="10">
+        <v>4900</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J31" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F32" s="8">
+        <v>11</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H32" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I32" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J32" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33" s="7" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F33" s="8">
+        <v>7</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H33" s="10">
+        <v>4900</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J33" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F34" s="8">
+        <v>11</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H34" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I34" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J34" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="7" t="s">
+        <v>1312</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F35" s="8">
+        <v>11</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H35" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J35" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F36" s="8">
+        <v>12</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H36" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I36" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J36" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F37" s="8">
+        <v>10</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H37" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J37" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38" s="7" t="s">
+        <v>1313</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F38" s="8">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H38" s="10"/>
+      <c r="I38" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J38" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39" s="7" t="s">
+        <v>1314</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F39" s="8">
+        <v>11</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H39" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J39" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40" s="7" t="s">
+        <v>1315</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F40" s="8">
+        <v>13</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H40" s="10">
+        <v>14900</v>
+      </c>
+      <c r="I40" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J40" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="7" t="s">
+        <v>1316</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F41" s="8">
+        <v>10</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H41" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J41" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="7" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F42" s="8">
+        <v>16</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H42" s="10">
+        <v>24500</v>
+      </c>
+      <c r="I42" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J42" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43" s="7" t="s">
+        <v>1318</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F43" s="8">
+        <v>11</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H43" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J43" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44" s="7" t="s">
+        <v>1319</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F44" s="8">
+        <v>11</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H44" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I44" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J44" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45" s="7" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F45" s="8">
+        <v>16</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H45" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J45" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10">
+      <c r="B46" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F46" s="8">
+        <v>15</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H46" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I46" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J46" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10">
+      <c r="B47" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F47" s="8">
+        <v>1</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H47" s="10"/>
+      <c r="I47" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J47" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10">
+      <c r="B48" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F48" s="8">
+        <v>1</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H48" s="10"/>
+      <c r="I48" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J48" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:10">
+      <c r="B49" s="7" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F49" s="8">
+        <v>1</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H49" s="10"/>
+      <c r="I49" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J49" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:10">
+      <c r="B50" s="7" t="s">
+        <v>1322</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F50" s="8">
+        <v>1</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H50" s="10"/>
+      <c r="I50" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J50" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10">
+      <c r="B51" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F51" s="8">
+        <v>1</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H51" s="10"/>
+      <c r="I51" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J51" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:10">
+      <c r="B52" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F52" s="8">
+        <v>1</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H52" s="10"/>
+      <c r="I52" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J52" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:10">
+      <c r="B53" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F53" s="8">
+        <v>1</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H53" s="10"/>
+      <c r="I53" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J53" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:10">
+      <c r="B54" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F54" s="8">
+        <v>1</v>
+      </c>
+      <c r="G54" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H54" s="10"/>
+      <c r="I54" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J54" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:10">
+      <c r="B55" s="7" t="s">
+        <v>1323</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F55" s="8">
+        <v>12</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H55" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I55" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J55" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:10">
+      <c r="B56" s="7" t="s">
+        <v>1324</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F56" s="8">
+        <v>11</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H56" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I56" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J56" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:10">
+      <c r="B57" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F57" s="8">
+        <v>6</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>1326</v>
+      </c>
+      <c r="H57" s="10">
+        <v>36500</v>
+      </c>
+      <c r="I57" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J57" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:10">
+      <c r="B58" s="7" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F58" s="8">
+        <v>11</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H58" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I58" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J58" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:10">
+      <c r="B59" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F59" s="8">
+        <v>6</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H59" s="10">
+        <v>9000</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J59" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:10">
+      <c r="B60" s="7" t="s">
+        <v>1328</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F60" s="8">
+        <v>10</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H60" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J60" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:10">
+      <c r="B61" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F61" s="8">
+        <v>6</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H61" s="10">
+        <v>6500</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J61" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:10">
+      <c r="B62" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F62" s="8">
+        <v>11</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H62" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J62" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:10">
+      <c r="B63" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F63" s="8">
+        <v>2</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H63" s="10"/>
+      <c r="I63" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J63" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:10">
+      <c r="B64" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F64" s="8">
+        <v>2</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H64" s="10"/>
+      <c r="I64" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J64" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:10">
+      <c r="B65" s="7" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F65" s="8">
+        <v>2</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H65" s="10"/>
+      <c r="I65" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J65" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10">
+      <c r="B66" s="7" t="s">
+        <v>1333</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F66" s="8">
+        <v>2</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H66" s="10"/>
+      <c r="I66" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J66" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:10">
+      <c r="B67" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F67" s="8">
+        <v>2</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H67" s="10"/>
+      <c r="I67" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J67" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10">
+      <c r="B68" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F68" s="8">
+        <v>1</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H68" s="10"/>
+      <c r="I68" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J68" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="2:10">
+      <c r="B69" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F69" s="8">
+        <v>2</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H69" s="10"/>
+      <c r="I69" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J69" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10">
+      <c r="B70" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F70" s="8">
+        <v>2</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H70" s="10"/>
+      <c r="I70" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J70" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="2:10">
+      <c r="B71" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="F71" s="8">
+        <v>2</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H71" s="10"/>
+      <c r="I71" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J71" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="2:10">
+      <c r="B72" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E72" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F72" s="8">
+        <v>11</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H72" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I72" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J72" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="2:10">
+      <c r="B73" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E73" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F73" s="8">
+        <v>11</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H73" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I73" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J73" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="2:10">
+      <c r="B74" s="7" t="s">
+        <v>1334</v>
+      </c>
+      <c r="C74" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F74" s="8">
+        <v>1</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H74" s="10"/>
+      <c r="I74" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J74" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="2:10">
+      <c r="B75" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C75" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D75" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E75" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F75" s="8">
+        <v>1</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H75" s="10"/>
+      <c r="I75" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J75" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="2:10">
+      <c r="B76" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C76" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D76" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E76" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F76" s="8">
+        <v>1</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H76" s="10"/>
+      <c r="I76" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J76" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:10">
+      <c r="B77" s="7" t="s">
+        <v>1335</v>
+      </c>
+      <c r="C77" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D77" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F77" s="8">
+        <v>1</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H77" s="10"/>
+      <c r="I77" s="7" t="s">
+        <v>1283</v>
+      </c>
+      <c r="J77" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:10">
+      <c r="B78" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C78" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F78" s="8">
+        <v>11</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H78" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I78" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J78" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="2:10">
+      <c r="B79" s="7" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C79" s="7" t="s">
+        <v>1280</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E79" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F79" s="8">
+        <v>2</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H79" s="10"/>
+      <c r="I79" s="7" t="s">
+        <v>1302</v>
+      </c>
+      <c r="J79" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:10">
+      <c r="B80" s="7" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F80" s="8">
+        <v>2</v>
+      </c>
+      <c r="G80" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H80" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I80" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J80" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:10">
+      <c r="B81" s="7" t="s">
+        <v>1338</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F81" s="8">
+        <v>11</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H81" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I81" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J81" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="2:10">
+      <c r="B82" s="7" t="s">
+        <v>1339</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E82" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F82" s="8">
+        <v>7</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H82" s="10">
+        <v>27000</v>
+      </c>
+      <c r="I82" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J82" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="2:10">
+      <c r="B83" s="7" t="s">
+        <v>1340</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E83" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F83" s="8">
+        <v>3</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H83" s="10">
+        <v>1900</v>
+      </c>
+      <c r="I83" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J83" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:10">
+      <c r="B84" s="7" t="s">
+        <v>1341</v>
+      </c>
+      <c r="C84" s="7" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D84" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E84" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F84" s="8">
+        <v>1</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="H84" s="10">
+        <v>250</v>
+      </c>
+      <c r="I84" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J84" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:10">
+      <c r="B85" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E85" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F85" s="8">
+        <v>7</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H85" s="10">
+        <v>4900</v>
+      </c>
+      <c r="I85" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J85" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="2:10">
+      <c r="B86" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E86" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F86" s="8">
+        <v>10</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H86" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I86" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J86" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:10">
+      <c r="B87" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E87" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F87" s="8">
+        <v>11</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H87" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J87" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="2:10">
+      <c r="B88" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F88" s="8">
+        <v>10</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H88" s="10">
+        <v>14900</v>
+      </c>
+      <c r="I88" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J88" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="2:10">
+      <c r="B89" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E89" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F89" s="8">
+        <v>10</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H89" s="10">
+        <v>19750</v>
+      </c>
+      <c r="I89" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J89" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="2:10">
+      <c r="B90" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E90" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F90" s="8">
+        <v>6</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H90" s="10">
+        <v>6500</v>
+      </c>
+      <c r="I90" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J90" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="2:10">
+      <c r="B91" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F91" s="8">
+        <v>7</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H91" s="10">
+        <v>27000</v>
+      </c>
+      <c r="I91" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J91" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="2:10">
+      <c r="B92" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E92" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F92" s="8">
+        <v>9</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H92" s="10">
+        <v>10900</v>
+      </c>
+      <c r="I92" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J92" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="2:10">
+      <c r="B93" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E93" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F93" s="8">
+        <v>10</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H93" s="10">
+        <v>13500</v>
+      </c>
+      <c r="I93" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J93" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="2:10">
+      <c r="B94" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F94" s="8">
+        <v>11</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H94" s="10">
+        <v>16500</v>
+      </c>
+      <c r="I94" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J94" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:10">
+      <c r="B95" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F95" s="8">
+        <v>8</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="H95" s="10">
+        <v>9900</v>
+      </c>
+      <c r="I95" s="7" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J95" s="8">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:B38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5915,17 +8605,17 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>1306</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" s="5" t="s">
-        <v>1307</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" s="9" t="s">
-        <v>1308</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="7" spans="2:2">
@@ -5936,12 +8626,12 @@
     </row>
     <row r="10" spans="2:2">
       <c r="B10" s="5" t="s">
-        <v>1309</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" s="9" t="s">
-        <v>1310</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="12" spans="2:2">
@@ -5952,12 +8642,12 @@
     </row>
     <row r="15" spans="2:2">
       <c r="B15" s="5" t="s">
-        <v>1311</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" s="9" t="s">
-        <v>1312</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="17" spans="2:2">
@@ -5968,12 +8658,12 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="5" t="s">
-        <v>1313</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="9" t="s">
-        <v>1314</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="22" spans="2:2">
@@ -5984,12 +8674,12 @@
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="5" t="s">
-        <v>1315</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" s="9" t="s">
-        <v>1316</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="27" spans="2:2">
@@ -6000,12 +8690,12 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="5" t="s">
-        <v>1317</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="9" t="s">
-        <v>1318</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="32" spans="2:2">
@@ -6016,12 +8706,12 @@
     </row>
     <row r="35" spans="2:2">
       <c r="B35" s="5" t="s">
-        <v>1319</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="36" spans="2:2">
       <c r="B36" s="9" t="s">
-        <v>1320</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="37" spans="2:2">
@@ -6784,7 +9474,7 @@
       </c>
       <c r="E18" s="10"/>
       <c r="F18" s="8">
-        <v>15700</v>
+        <v>15646</v>
       </c>
       <c r="G18" s="8">
         <v>6527</v>
@@ -6797,14 +9487,14 @@
         <v>69</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="8">
-        <v>15646</v>
+        <v>15756</v>
       </c>
       <c r="G19" s="8">
         <v>6527</v>
@@ -6814,17 +9504,17 @@
     </row>
     <row r="20" spans="2:9">
       <c r="B20" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>55</v>
       </c>
       <c r="E20" s="10"/>
       <c r="F20" s="8">
-        <v>15756</v>
+        <v>15700</v>
       </c>
       <c r="G20" s="8">
         <v>6527</v>
@@ -6863,7 +9553,7 @@
         <v>73</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>55</v>
@@ -6958,7 +9648,7 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="7" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>61</v>
@@ -6968,7 +9658,7 @@
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="8">
-        <v>15865</v>
+        <v>15855</v>
       </c>
       <c r="G26" s="8">
         <v>6507</v>
@@ -6978,7 +9668,7 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="7" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>61</v>
@@ -6988,7 +9678,7 @@
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="8">
-        <v>15855</v>
+        <v>15865</v>
       </c>
       <c r="G27" s="8">
         <v>6507</v>
@@ -7197,7 +9887,7 @@
         <v>86</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>62</v>
@@ -14628,2566 +17318,198 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:J95"/>
+  <dimension ref="B2:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
-    <col min="2" max="2" width="52.7109375" customWidth="1"/>
-    <col min="3" max="3" width="24.7109375" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" customWidth="1"/>
-    <col min="6" max="6" width="17.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
-    <col min="8" max="8" width="21.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="10" max="10" width="21.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" customWidth="1"/>
+    <col min="3" max="3" width="54.7109375" customWidth="1"/>
+    <col min="4" max="4" width="62.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="44.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10">
+    <row r="2" spans="2:7">
       <c r="B2" s="1" t="s">
         <v>1231</v>
       </c>
     </row>
-    <row r="3" spans="2:10">
+    <row r="3" spans="2:7">
       <c r="B3" s="2" t="s">
         <v>1232</v>
       </c>
     </row>
-    <row r="6" spans="2:10" ht="30" customHeight="1">
+    <row r="6" spans="2:7" ht="30" customHeight="1">
       <c r="B6" s="6" t="s">
-        <v>48</v>
+        <v>1215</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>49</v>
+        <v>1233</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>50</v>
+        <v>1234</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>1235</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="6" t="s">
         <v>1236</v>
       </c>
-      <c r="J6" s="6" t="s">
+    </row>
+    <row r="7" spans="2:7">
+      <c r="B7" s="7" t="s">
         <v>1237</v>
       </c>
-    </row>
-    <row r="7" spans="2:10">
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
         <v>1238</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="D7" s="7" t="s">
         <v>1239</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E7" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>1240</v>
       </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="7" t="s">
+    </row>
+    <row r="8" spans="2:7">
+      <c r="B8" s="7" t="s">
         <v>1241</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="7" t="s">
+      <c r="C8" s="7" t="s">
         <v>1242</v>
       </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" s="7" t="s">
+      <c r="D8" s="7" t="s">
         <v>1243</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E8" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F8" s="8">
-        <v>7</v>
-      </c>
-      <c r="G8" s="7" t="s">
+        <v>1241</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>1244</v>
       </c>
-      <c r="H8" s="10">
-        <v>27000</v>
-      </c>
-      <c r="I8" s="7" t="s">
+    </row>
+    <row r="9" spans="2:7">
+      <c r="B9" s="7" t="s">
         <v>1245</v>
       </c>
-      <c r="J8" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10">
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
         <v>1246</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>1247</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="E9" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F9" s="8">
-        <v>2</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H9" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I9" s="7" t="s">
         <v>1245</v>
       </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10">
+      <c r="F9" s="7" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7">
       <c r="B10" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>55</v>
+        <v>1251</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J10" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10">
+        <v>1252</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7">
       <c r="B11" s="7" t="s">
-        <v>1249</v>
+        <v>1254</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1247</v>
+        <v>1255</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>55</v>
+        <v>1256</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H11" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10">
+        <v>1257</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7">
       <c r="B12" s="7" t="s">
-        <v>1250</v>
+        <v>1259</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1247</v>
+        <v>1260</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>55</v>
+        <v>1261</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F12" s="8">
-        <v>2</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H12" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J12" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10">
-      <c r="B13" s="7" t="s">
-        <v>1251</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F13" s="8">
-        <v>2</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H13" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10">
-      <c r="B14" s="7" t="s">
-        <v>1252</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F14" s="8">
-        <v>2</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H14" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J14" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10">
-      <c r="B15" s="7" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F15" s="8">
-        <v>2</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H15" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10">
-      <c r="B16" s="7" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F16" s="8">
-        <v>13</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H16" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J16" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" s="7" t="s">
-        <v>1255</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F17" s="8">
-        <v>1</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H17" s="10"/>
-      <c r="I17" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="7" t="s">
-        <v>1257</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F18" s="8">
-        <v>1</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H18" s="10"/>
-      <c r="I18" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J18" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="7" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F19" s="8">
-        <v>1</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H19" s="10"/>
-      <c r="I19" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J19" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="7" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F20" s="8">
-        <v>11</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H20" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J20" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="7" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="7" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J21" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="7" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F22" s="8">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H22" s="10"/>
-      <c r="I22" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J22" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="7" t="s">
         <v>1262</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="F12" s="7" t="s">
         <v>1263</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F23" s="8">
-        <v>3</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H23" s="10"/>
-      <c r="I23" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J23" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:10">
-      <c r="B24" s="7" t="s">
+    </row>
+    <row r="14" spans="2:7">
+      <c r="B14" s="5" t="s">
         <v>1264</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F24" s="8">
-        <v>3</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H24" s="10"/>
-      <c r="I24" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J24" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:10">
-      <c r="B25" s="7" t="s">
+    </row>
+    <row r="15" spans="2:7">
+      <c r="B15" s="5" t="s">
         <v>1265</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="7" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J25" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:10">
-      <c r="B26" s="7" t="s">
+      <c r="C15" s="9" t="s">
         <v>1266</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F26" s="8">
-        <v>3</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H26" s="10"/>
-      <c r="I26" s="7" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J26" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:10">
-      <c r="B27" s="7" t="s">
-        <v>1266</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F27" s="8">
-        <v>3</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J27" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:10">
-      <c r="B28" s="7" t="s">
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="2:7">
+      <c r="B16" s="5" t="s">
         <v>1267</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F28" s="8">
-        <v>7</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H28" s="10">
-        <v>27000</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J28" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="2:10">
-      <c r="B29" s="7" t="s">
+      <c r="C16" s="9" t="s">
         <v>1268</v>
       </c>
-      <c r="C29" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F29" s="8">
-        <v>14</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H29" s="10">
-        <v>14900</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J29" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10">
-      <c r="B30" s="7" t="s">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="2:7">
+      <c r="B17" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F30" s="8">
-        <v>11</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H30" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J30" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10">
-      <c r="B31" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F31" s="8">
-        <v>7</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H31" s="10">
-        <v>4900</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J31" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10">
-      <c r="B32" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F32" s="8">
-        <v>11</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H32" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J32" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10">
-      <c r="B33" s="7" t="s">
+      <c r="C17" s="9" t="s">
         <v>1270</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F33" s="8">
-        <v>7</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H33" s="10">
-        <v>4900</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J33" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10">
-      <c r="B34" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F34" s="8">
-        <v>11</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H34" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J34" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:10">
-      <c r="B35" s="7" t="s">
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+    </row>
+    <row r="19" spans="2:7">
+      <c r="B19" s="13" t="s">
         <v>1271</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F35" s="8">
-        <v>11</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H35" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J35" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:10">
-      <c r="B36" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F36" s="8">
-        <v>12</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H36" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I36" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J36" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="2:10">
-      <c r="B37" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F37" s="8">
-        <v>10</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H37" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J37" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10">
-      <c r="B38" s="7" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F38" s="8">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H38" s="10"/>
-      <c r="I38" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J38" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:10">
-      <c r="B39" s="7" t="s">
-        <v>1273</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F39" s="8">
-        <v>11</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H39" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J39" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10">
-      <c r="B40" s="7" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F40" s="8">
-        <v>13</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H40" s="10">
-        <v>14900</v>
-      </c>
-      <c r="I40" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J40" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10">
-      <c r="B41" s="7" t="s">
-        <v>1275</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F41" s="8">
-        <v>10</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H41" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J41" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:10">
-      <c r="B42" s="7" t="s">
-        <v>1276</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F42" s="8">
-        <v>16</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H42" s="10">
-        <v>24500</v>
-      </c>
-      <c r="I42" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J42" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="2:10">
-      <c r="B43" s="7" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F43" s="8">
-        <v>11</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H43" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J43" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:10">
-      <c r="B44" s="7" t="s">
-        <v>1278</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F44" s="8">
-        <v>11</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H44" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I44" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J44" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:10">
-      <c r="B45" s="7" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F45" s="8">
-        <v>16</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H45" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J45" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:10">
-      <c r="B46" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D46" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F46" s="8">
-        <v>15</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H46" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I46" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J46" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:10">
-      <c r="B47" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F47" s="8">
-        <v>1</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H47" s="10"/>
-      <c r="I47" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J47" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="2:10">
-      <c r="B48" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E48" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F48" s="8">
-        <v>1</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H48" s="10"/>
-      <c r="I48" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J48" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:10">
-      <c r="B49" s="7" t="s">
-        <v>1280</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F49" s="8">
-        <v>1</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H49" s="10"/>
-      <c r="I49" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J49" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:10">
-      <c r="B50" s="7" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E50" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F50" s="8">
-        <v>1</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H50" s="10"/>
-      <c r="I50" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J50" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:10">
-      <c r="B51" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F51" s="8">
-        <v>1</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J51" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="2:10">
-      <c r="B52" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F52" s="8">
-        <v>1</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H52" s="10"/>
-      <c r="I52" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J52" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="2:10">
-      <c r="B53" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F53" s="8">
-        <v>1</v>
-      </c>
-      <c r="G53" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J53" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="2:10">
-      <c r="B54" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D54" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F54" s="8">
-        <v>1</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H54" s="10"/>
-      <c r="I54" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J54" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="2:10">
-      <c r="B55" s="7" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D55" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F55" s="8">
-        <v>12</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H55" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I55" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J55" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:10">
-      <c r="B56" s="7" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F56" s="8">
-        <v>11</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H56" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I56" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J56" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="2:10">
-      <c r="B57" s="7" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D57" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F57" s="8">
-        <v>6</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>1285</v>
-      </c>
-      <c r="H57" s="10">
-        <v>36500</v>
-      </c>
-      <c r="I57" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J57" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="2:10">
-      <c r="B58" s="7" t="s">
-        <v>1286</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F58" s="8">
-        <v>11</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H58" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I58" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J58" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:10">
-      <c r="B59" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F59" s="8">
-        <v>6</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H59" s="10">
-        <v>9000</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J59" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="2:10">
-      <c r="B60" s="7" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F60" s="8">
-        <v>10</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H60" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J60" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="2:10">
-      <c r="B61" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F61" s="8">
-        <v>6</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H61" s="10">
-        <v>6500</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J61" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="2:10">
-      <c r="B62" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F62" s="8">
-        <v>11</v>
-      </c>
-      <c r="G62" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H62" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J62" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="2:10">
-      <c r="B63" s="7" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F63" s="8">
-        <v>2</v>
-      </c>
-      <c r="G63" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J63" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:10">
-      <c r="B64" s="7" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F64" s="8">
-        <v>2</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H64" s="10"/>
-      <c r="I64" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J64" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:10">
-      <c r="B65" s="7" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F65" s="8">
-        <v>2</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H65" s="10"/>
-      <c r="I65" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J65" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:10">
-      <c r="B66" s="7" t="s">
-        <v>1292</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>1256</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F66" s="8">
-        <v>2</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H66" s="10"/>
-      <c r="I66" s="7" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J66" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:10">
-      <c r="B67" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F67" s="8">
-        <v>2</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H67" s="10"/>
-      <c r="I67" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J67" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10">
-      <c r="B68" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D68" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F68" s="8">
-        <v>1</v>
-      </c>
-      <c r="G68" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H68" s="10"/>
-      <c r="I68" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J68" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10">
-      <c r="B69" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D69" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F69" s="8">
-        <v>2</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H69" s="10"/>
-      <c r="I69" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J69" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10">
-      <c r="B70" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D70" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F70" s="8">
-        <v>2</v>
-      </c>
-      <c r="G70" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H70" s="10"/>
-      <c r="I70" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J70" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="2:10">
-      <c r="B71" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C71" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E71" s="7" t="s">
-        <v>1289</v>
-      </c>
-      <c r="F71" s="8">
-        <v>2</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H71" s="10"/>
-      <c r="I71" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J71" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="2:10">
-      <c r="B72" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C72" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D72" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E72" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F72" s="8">
-        <v>11</v>
-      </c>
-      <c r="G72" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H72" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I72" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J72" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="2:10">
-      <c r="B73" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C73" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D73" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E73" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F73" s="8">
-        <v>11</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H73" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I73" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J73" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="2:10">
-      <c r="B74" s="7" t="s">
-        <v>1293</v>
-      </c>
-      <c r="C74" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D74" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E74" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F74" s="8">
-        <v>1</v>
-      </c>
-      <c r="G74" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H74" s="10"/>
-      <c r="I74" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J74" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="2:10">
-      <c r="B75" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C75" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D75" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E75" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F75" s="8">
-        <v>1</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J75" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="2:10">
-      <c r="B76" s="7" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C76" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D76" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E76" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F76" s="8">
-        <v>1</v>
-      </c>
-      <c r="G76" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H76" s="10"/>
-      <c r="I76" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J76" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:10">
-      <c r="B77" s="7" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C77" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D77" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E77" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F77" s="8">
-        <v>1</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H77" s="10"/>
-      <c r="I77" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="J77" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:10">
-      <c r="B78" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D78" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E78" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F78" s="8">
-        <v>11</v>
-      </c>
-      <c r="G78" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H78" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I78" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J78" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="2:10">
-      <c r="B79" s="7" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C79" s="7" t="s">
-        <v>1239</v>
-      </c>
-      <c r="D79" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E79" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F79" s="8">
-        <v>2</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>1241</v>
-      </c>
-      <c r="H79" s="10"/>
-      <c r="I79" s="7" t="s">
-        <v>1261</v>
-      </c>
-      <c r="J79" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:10">
-      <c r="B80" s="7" t="s">
-        <v>1296</v>
-      </c>
-      <c r="C80" s="7" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D80" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E80" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F80" s="8">
-        <v>2</v>
-      </c>
-      <c r="G80" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H80" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I80" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J80" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:10">
-      <c r="B81" s="7" t="s">
-        <v>1297</v>
-      </c>
-      <c r="C81" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D81" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E81" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F81" s="8">
-        <v>11</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H81" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I81" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J81" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="2:10">
-      <c r="B82" s="7" t="s">
-        <v>1298</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F82" s="8">
-        <v>7</v>
-      </c>
-      <c r="G82" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H82" s="10">
-        <v>27000</v>
-      </c>
-      <c r="I82" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J82" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="2:10">
-      <c r="B83" s="7" t="s">
-        <v>1299</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F83" s="8">
-        <v>3</v>
-      </c>
-      <c r="G83" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H83" s="10">
-        <v>1900</v>
-      </c>
-      <c r="I83" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J83" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:10">
-      <c r="B84" s="7" t="s">
-        <v>1300</v>
-      </c>
-      <c r="C84" s="7" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D84" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E84" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F84" s="8">
-        <v>1</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>1301</v>
-      </c>
-      <c r="H84" s="10">
-        <v>250</v>
-      </c>
-      <c r="I84" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J84" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:10">
-      <c r="B85" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F85" s="8">
-        <v>7</v>
-      </c>
-      <c r="G85" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H85" s="10">
-        <v>4900</v>
-      </c>
-      <c r="I85" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J85" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="2:10">
-      <c r="B86" s="7" t="s">
-        <v>1302</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F86" s="8">
-        <v>10</v>
-      </c>
-      <c r="G86" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H86" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I86" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J86" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:10">
-      <c r="B87" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F87" s="8">
-        <v>11</v>
-      </c>
-      <c r="G87" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H87" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J87" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="2:10">
-      <c r="B88" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F88" s="8">
-        <v>10</v>
-      </c>
-      <c r="G88" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H88" s="10">
-        <v>14900</v>
-      </c>
-      <c r="I88" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J88" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="2:10">
-      <c r="B89" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F89" s="8">
-        <v>10</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H89" s="10">
-        <v>19750</v>
-      </c>
-      <c r="I89" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J89" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="2:10">
-      <c r="B90" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F90" s="8">
-        <v>6</v>
-      </c>
-      <c r="G90" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H90" s="10">
-        <v>6500</v>
-      </c>
-      <c r="I90" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J90" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="2:10">
-      <c r="B91" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F91" s="8">
-        <v>7</v>
-      </c>
-      <c r="G91" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H91" s="10">
-        <v>27000</v>
-      </c>
-      <c r="I91" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J91" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="2:10">
-      <c r="B92" s="7" t="s">
-        <v>1303</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F92" s="8">
-        <v>9</v>
-      </c>
-      <c r="G92" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H92" s="10">
-        <v>10900</v>
-      </c>
-      <c r="I92" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J92" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="2:10">
-      <c r="B93" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F93" s="8">
-        <v>10</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H93" s="10">
-        <v>13500</v>
-      </c>
-      <c r="I93" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J93" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="2:10">
-      <c r="B94" s="7" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F94" s="8">
-        <v>11</v>
-      </c>
-      <c r="G94" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H94" s="10">
-        <v>16500</v>
-      </c>
-      <c r="I94" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J94" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:10">
-      <c r="B95" s="7" t="s">
-        <v>1305</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F95" s="8">
-        <v>8</v>
-      </c>
-      <c r="G95" s="7" t="s">
-        <v>1244</v>
-      </c>
-      <c r="H95" s="10">
-        <v>9900</v>
-      </c>
-      <c r="I95" s="7" t="s">
-        <v>1245</v>
-      </c>
-      <c r="J95" s="8">
-        <v>0</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/reporting/RedAndYellow_Analytics.xlsx
+++ b/reporting/RedAndYellow_Analytics.xlsx
@@ -248,12 +248,12 @@
     <t>Part-Time Postgraduate Diploma in Management</t>
   </si>
   <si>
+    <t>Creative Thinking</t>
+  </si>
+  <si>
     <t>Design Thinking</t>
   </si>
   <si>
-    <t>Creative Thinking</t>
-  </si>
-  <si>
     <t>People Management</t>
   </si>
   <si>
@@ -3806,10 +3806,10 @@
     <t>Platform</t>
   </si>
   <si>
-    <t>Fabric silver/gold and GA4 remain gated by external execution.</t>
-  </si>
-  <si>
-    <t>Fix T-SQL compatibility, rerun dbt in Fabric, then add GA4 as dated bronze.</t>
+    <t>Fabric silver/gold remains gated by external execution; GA4 can use the Data API without BigQuery or native BigQuery export for raw events.</t>
+  </si>
+  <si>
+    <t>Keep the Data API route for aggregated campaign KPIs; use native BigQuery export for raw events, then run the shared dbt graph on the BigQuery target.</t>
   </si>
   <si>
     <t>Data engineering</t>
@@ -6752,7 +6752,7 @@
     </row>
     <row r="31" spans="2:10">
       <c r="B31" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>54</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="37" spans="2:10">
       <c r="B37" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>54</v>
@@ -9579,19 +9579,19 @@
         <v>55</v>
       </c>
       <c r="E23" s="10">
-        <v>13500</v>
+        <v>4900</v>
       </c>
       <c r="F23" s="8">
-        <v>15794</v>
+        <v>15795</v>
       </c>
       <c r="G23" s="8">
         <v>6516</v>
       </c>
       <c r="H23" s="12">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="I23" s="10">
-        <v>72441283</v>
+        <v>26454867</v>
       </c>
     </row>
     <row r="24" spans="2:9">
@@ -9605,19 +9605,19 @@
         <v>55</v>
       </c>
       <c r="E24" s="10">
-        <v>4900</v>
+        <v>13500</v>
       </c>
       <c r="F24" s="8">
-        <v>15795</v>
+        <v>15794</v>
       </c>
       <c r="G24" s="8">
         <v>6516</v>
       </c>
       <c r="H24" s="12">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="I24" s="10">
-        <v>26454867</v>
+        <v>72441283</v>
       </c>
     </row>
     <row r="25" spans="2:9">
@@ -9648,7 +9648,7 @@
     </row>
     <row r="26" spans="2:9">
       <c r="B26" s="7" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>61</v>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="E26" s="10"/>
       <c r="F26" s="8">
-        <v>15855</v>
+        <v>15865</v>
       </c>
       <c r="G26" s="8">
         <v>6507</v>
@@ -9668,7 +9668,7 @@
     </row>
     <row r="27" spans="2:9">
       <c r="B27" s="7" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>61</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="8">
-        <v>15865</v>
+        <v>15855</v>
       </c>
       <c r="G27" s="8">
         <v>6507</v>
